--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="물가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="고용" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="성장" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="유가" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="금리" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유가" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금리" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1226,6 +1226,24 @@
       </c>
       <c r="C61" t="n">
         <v>3.12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -2941,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3783,16 +3783,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B76" t="n">
         <v>3</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4.45</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -1257,13 +1257,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2066,6 +2066,24 @@
       </c>
       <c r="C61" t="n">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>29266</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -2333,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2946,6 +2946,26 @@
       </c>
       <c r="B60" t="n">
         <v>77.1318</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>88.05329999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>111.8252</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/korea.xlsx
+++ b/site/data/downloads/korea.xlsx
@@ -2097,12 +2097,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2320,6 +2320,21 @@
       </c>
       <c r="B21" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
       </c>
     </row>
   </sheetData>
